--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer, II - Data Engineering</t>
+          <t>Solutions Architect (Cloud Transformation)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
+          <t>https://www.indeed.com/viewjob?jk=e1bf1acae957760a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Software Engineer, II - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ad84a4ec3d68d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
+          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,122 +626,122 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Developer (Sr. Software Development Engineer)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, IAM, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
+          <t>https://www.indeed.com/viewjob?jk=022f538ee963f0fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Quality and Productivity</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
+          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wyoming, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639ed0412b5015c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Centerfield</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DataBricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Event Network, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
+          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Event Network, LLC</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Grading Operations</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Kafka, SQL Server, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d3a613ac15910d</t>
+          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Boston, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9668a782d26f23f2</t>
+          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80fb7f5a0962d33</t>
+          <t>https://www.indeed.com/viewjob?jk=9668a782d26f23f2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c80fb7f5a0962d33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Governance Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>AIT Worldwide Logistics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Enterprise Architect, Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Developer (ETL)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Health Care Payer Domain</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
+          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Developer (ETL)</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
+          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
+          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
+          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
+          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>STATE WATER RESOURCES CONTROL BOARD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>STATE WATER RESOURCES CONTROL BOARD</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
+          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (DataLake to AWS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (DataLake to AWS)</t>
+          <t>Senior Advisor II, Application Architecture- Refining</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
+          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,137 +2526,137 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rakuten International</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
+          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Python/AWS)</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c218f1db2c299ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Summer 2027 Feature Engineer Internship</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product Analytics</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Summer 2027 Feature Engineer Internship</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Senior Analytics Engineer, Product Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Beckett</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, RDS, PostgreSQL, MySQL, CI/CD, CodeBuild, Terraform</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b0c15a37577d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer - Application Development</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Allegiant Air</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Data Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Innovation Associates, Inc.</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Binghamton, NY, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (DevOps)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Data &amp; AI Platform Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior AI Systems Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Binghamton, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Group AI Technical Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lancaster, OH, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MLOps, Docker, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=967c27da9f0d8c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cybersecurity Automation Engineer III</t>
+          <t>Infrastructure Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
+          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AWS Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36cf23d5a5bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ELEVI Associates, LLC</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,155 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cybersecurity Automation Engineer III</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hard Rock International</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Davie, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr ML Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=198a1af082f7d7e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ELEVI Associates, LLC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Annapolis Junction, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
         </is>

--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, II - Data Engineering</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
+          <t>https://www.indeed.com/viewjob?jk=aface31a02c74f0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,77 +566,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9faddc3559ec4193</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Software Engineer, II - Data Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
+          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Centerfield</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Java Developer, Officer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect Consultant</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data &amp; Reporting Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Medvantx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
+          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Reporting Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medvantx</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Connectedx, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
+          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Databricks Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Architect (Onsite Hybrid)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
+          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer, Payment Data Intelligence</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
+          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Payment Data Intelligence</t>
+          <t>Data Engineer - Office-Based in Minnesota</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Office-Based in Minnesota</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer (DataLake to AWS)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (DataLake to AWS)</t>
+          <t>Senior Advisor II, Application Architecture- Refining</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
+          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Application Architecture- Refining</t>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bartlesville, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Mid-level Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=30a34e7333233154</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Summer 2027 Feature Engineer Internship</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer Sr.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Donaldson</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Analytics Engineer, Product Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Summer 2027 Feature Engineer Internship</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product Analytics</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Oracle Senior Python and Kafka Engineer</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Supply Chain Data Analytics</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
+          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Sr. Analyst, Supply Chain Data Analytics</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INFO IMAGE</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brisbane, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer - Application Development</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
+          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (DevOps)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cybersecurity Automation Engineer III</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr ML Engineer</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, AL, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1af082f7d7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ELEVI Associates, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,297 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sr ML Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Boston, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=198a1af082f7d7e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Java AWS Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Cybersecurity Automation Engineer III</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hard Rock International</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Davie, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sr Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ELEVI Associates, LLC</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Annapolis Junction, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect (Cloud Transformation)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1bf1acae957760a</t>
+          <t>https://www.indeed.com/viewjob?jk=383bce16ad78ce6b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Solutions Architect (Cloud Transformation)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Personify Health</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>24.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aface31a02c74f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1bf1acae957760a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9faddc3559ec4193</t>
+          <t>https://www.indeed.com/viewjob?jk=aface31a02c74f0e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, II - Data Engineering</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
+          <t>https://www.indeed.com/viewjob?jk=9faddc3559ec4193</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer, II - Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
+          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Developer (Sr. Software Development Engineer)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, Kafka Connect</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022f538ee963f0fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Developer (Sr. Software Development Engineer)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=022f538ee963f0fc</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZipLiens</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3205953035ac9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>ZipLiens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3205953035ac9b3a</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend Java)</t>
+          <t>Software Engineer Consultant II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VAMS Technologies</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer Consultant II</t>
+          <t>Senior Software Engineer (Backend Java)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>VAMS Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
+          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Java Developer, Officer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Event Network, LLC</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
+          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Event Network, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
+          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Reporting Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Medvantx</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data &amp; Reporting Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Medvantx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
+          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Architect (Onsite Hybrid)</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Connectedx, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
+          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
+          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
+          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
+          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mid-level Software Development Engineer in Test</t>
+          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a34e7333233154</t>
+          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
+          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer Sr.</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Donaldson</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Summer 2027 Feature Engineer Internship</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product Analytics</t>
+          <t>Summer 2027 Feature Engineer Internship</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
+          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Senior Analytics Engineer, Product Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Sr. Analyst, Supply Chain Data Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
+          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Oracle Senior Python and Kafka Engineer</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Supply Chain Data Analytics</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
+          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INFO IMAGE</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brisbane, CA, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer - Application Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Allegiant Air</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI Systems Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Data Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Innovation Associates, Inc.</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Binghamton, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Systems Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Binghamton, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Data &amp; AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
+          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
+          <t>Senior Architect Data Management</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Cybersecurity Automation Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr ML Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ELEVI Associates, LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, AL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
+          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1af082f7d7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3925,146 +3925,6 @@
         </is>
       </c>
       <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Cybersecurity Automation Engineer III</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Hard Rock International</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>ELEVI Associates, LLC</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Annapolis Junction, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
         </is>

--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer Consultant II</t>
+          <t>Senior Software Engineer (Backend Java)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>VAMS Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
+          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend Java)</t>
+          <t>Software Engineer Consultant II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VAMS Technologies</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Connectedx, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
+          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
+          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Governance Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AIT Worldwide Logistics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, CT, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect, Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9668a782d26f23f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Developer (ETL)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80fb7f5a0962d33</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AIT Worldwide Logistics</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
+          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Health Care Payer Domain</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
+          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Developer (ETL)</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
+          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
+          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
+          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
+          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
+          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>STATE WATER RESOURCES CONTROL BOARD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
+          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
+          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (DataLake to AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Advisor II, Application Architecture- Refining</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>STATE WATER RESOURCES CONTROL BOARD</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
+          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer, Payment Data Intelligence</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Office-Based in Minnesota</t>
+          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
+          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (DataLake to AWS)</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,46 +2302,46 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Application Architecture- Refining</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bartlesville, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+          <t>Summer 2027 Feature Engineer Internship</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Senior Analytics Engineer, Product Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer Sr.</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Donaldson</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
+          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Summer 2027 Feature Engineer Internship</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Oracle Senior Python and Kafka Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Supply Chain Data Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior AI Systems Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Architect Data Management</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
+          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cybersecurity Automation Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INFO IMAGE</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brisbane, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer - Application Development</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>ELEVI Associates, LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,497 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Allegiant Air</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CloudZero</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Software Data Engineering Intern</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Innovation Associates, Inc.</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Binghamton, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Architect Data Management</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Cybersecurity Automation Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Hard Rock International</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>ELEVI Associates, LLC</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Annapolis Junction, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Senior AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
+          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>ZipLiens</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3205953035ac9b3a</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZipLiens</t>
+          <t>Centerfield</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3205953035ac9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Backend Java)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>VAMS Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
+          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend Java)</t>
+          <t>Backend Java Developer, Officer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VAMS Technologies</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer Consultant II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
+          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Java Developer, Officer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Event Network, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
+          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Event Network, LLC</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect Consultant</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>Connectedx, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
+          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Reporting Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medvantx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Data Governance Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>AIT Worldwide Logistics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Enterprise Architect, Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
+          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Sr Data Developer (ETL)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, CT, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AIT Worldwide Logistics</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Health Care Payer Domain</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
+          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Developer (ETL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
+          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
+          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Analytics Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sudsies</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
+          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
+          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Advisor II, Application Architecture- Refining</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
+          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>STATE WATER RESOURCES CONTROL BOARD</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (DataLake to AWS)</t>
+          <t>Summer 2027 Feature Engineer Internship</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Application Architecture- Refining</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bartlesville, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer Sr.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Donaldson</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Summer 2027 Feature Engineer Internship</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Senior Architect Data Management</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle Senior Python and Kafka Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
+          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
+          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
+          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Cybersecurity Automation Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,567 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>INFO IMAGE</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Brisbane, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Engineer - Application Development</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>World Wide Technology</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Allegiant Air</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CloudZero</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Architect Data Management</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Cybersecurity Automation Engineer III</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Hard Rock International</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>ELEVI Associates, LLC</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Annapolis Junction, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, II - Data Engineering</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Developer (Sr. Software Development Engineer)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, S3, SNS, RDS, Databricks, GCP</t>
+          <t>AWS, IAM, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d13c40d6db3c55</t>
+          <t>https://www.indeed.com/viewjob?jk=022f538ee963f0fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Developer (Sr. Software Development Engineer)</t>
+          <t>Senior AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, Kafka Connect</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022f538ee963f0fc</t>
+          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Centerfield</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Java Developer, Officer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZipLiens</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3205953035ac9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
         </is>
       </c>
     </row>
@@ -788,55 +788,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
+          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend Java)</t>
+          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VAMS Technologies</t>
+          <t>Event Network, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Backend Java Developer, Officer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Connectedx, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Event Network, LLC</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect Consultant</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Governance Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>AIT Worldwide Logistics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Enterprise Architect, Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Sr Data Developer (ETL)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AIT Worldwide Logistics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
+          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Health Care Payer Domain</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
+          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Developer (ETL)</t>
+          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sudsies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
+          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Advisor II, Application Architecture- Refining</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
+          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Application Architecture- Refining</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bartlesville, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
+          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer Sr.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Donaldson</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Summer 2027 Feature Engineer Internship</t>
+          <t>Senior Architect Data Management</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Oracle Senior Python and Kafka Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
+          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
+          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
+          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Cybersecurity Automation Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,532 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Plymouth Meeting, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>INFO IMAGE</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Brisbane, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Engineer - Application Development</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>World Wide Technology</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Allegiant Air</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Architect Data Management</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Cybersecurity Automation Engineer III</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Hard Rock International</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-05.xlsx
+++ b/results/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,52 +748,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Java Developer, Officer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Event Network, LLC</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
+          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Data Governance Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>AIT Worldwide Logistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, IAM, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AIT Worldwide Logistics</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
+          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Health Care Payer Domain</t>
+          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc91fb4f404b6459</t>
+          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Developer (ETL)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,49 +1126,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Advisor II, Application Architecture- Refining</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sudsies</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
+          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform Foundations</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer Sr.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Donaldson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Application Architecture- Refining</t>
+          <t>Oracle Senior Python and Kafka Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bartlesville, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Software Engineer II - Platform Engineer Databricks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
+          <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer Sr.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Donaldson</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e60c32570d9101</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
+          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ecommerce Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Johnson Health Tech</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Oracle Senior Python and Kafka Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>INFO IMAGE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brisbane, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Kafka, Oracle, PostgreSQL, MongoDB, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d533ac255309b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Engineer - Application Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
+          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Architect Data Management</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83796b9ce5608df3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
+          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
+          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,392 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>INFO IMAGE</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Brisbane, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c17f8d478fe88a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Engineer - Application Development</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>World Wide Technology</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Architect Data Management</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc6345429532bcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Cybersecurity Automation Engineer III</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Hard Rock International</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
         </is>
       </c>
     </row>
